--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +804,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +824,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -854,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -887,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1053,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1109,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1153,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1524,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1572,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1567,7 +1591,7 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1603,7 +1627,788 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>3/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/13</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,14 +819,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>73.0</t>
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -872,24 +872,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1102,24 +1102,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1168,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1272,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1355,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1505,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1516,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1544,32 +1560,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1577,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1601,33 +1621,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1655,32 +1679,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1688,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,33 +1740,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1849,7 +1881,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1942,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1960,7 +1992,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2053,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2071,7 +2103,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2132,7 +2164,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2182,7 +2214,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2243,7 +2275,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2292,12 +2324,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2305,22 +2337,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2358,7 +2390,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2372,43 +2404,955 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>—/13</t>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1798,32 +1798,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1855,17 +1859,17 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -1875,13 +1879,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1981,7 +1989,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2053,7 +2061,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2164,7 +2172,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2275,7 +2283,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,7 +2398,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2513,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2616,7 +2624,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2739,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2842,7 +2850,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2965,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3072,7 +3080,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3183,7 +3191,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3237,7 +3245,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3306,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3352,7 +3360,118 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1053,18 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1570,24 +1578,24 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1597,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1646,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1716,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1765,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1808,24 +1816,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1835,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1917,32 +1925,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1950,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1974,17 +1986,17 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
@@ -1994,13 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2028,32 +2044,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2061,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2085,33 +2105,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2139,32 +2163,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2172,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2196,33 +2224,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2250,32 +2282,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:28</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2283,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2307,37 +2343,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2365,32 +2401,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2398,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2422,17 +2462,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2442,17 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2480,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2513,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2537,33 +2581,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2678,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2739,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2904,7 +2952,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2965,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3019,7 +3067,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3240,12 +3288,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3355,12 +3403,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3368,22 +3416,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3421,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3435,43 +3483,622 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>09:30</t>
         </is>
       </c>
-      <c r="V26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W26" s="2" t="inlineStr">
+      <c r="W27" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X26" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y26" s="2" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z26" s="2" t="inlineStr">
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>—/14</t>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,14 +823,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,13 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1887,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2135,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2254,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2373,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2477,14 +2481,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -2492,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2530,24 +2534,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2557,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,12 +2610,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2639,32 +2643,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2672,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2696,37 +2704,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2754,32 +2762,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -2787,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2811,33 +2823,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2865,32 +2881,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -2898,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2922,37 +2942,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2980,32 +3000,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3013,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3037,37 +3061,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3095,32 +3119,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -3128,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3152,17 +3180,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3172,13 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3206,32 +3238,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3239,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3263,37 +3299,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3321,32 +3357,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3354,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3378,32 +3418,32 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3436,32 +3476,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3469,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3493,17 +3537,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3513,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3551,32 +3595,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3584,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3608,17 +3656,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3628,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3738,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3753,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3868,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3983,7 +4031,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3991,22 +4039,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4044,7 +4092,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4058,47 +4106,967 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>87.0</t>
         </is>
       </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>4/14</t>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,12 +2724,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3498,12 +3498,12 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3605,24 +3605,24 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3681,12 +3681,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3714,32 +3714,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3747,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3771,17 +3775,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3791,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3916,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3944,32 +3948,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:07</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -3977,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,32 +4009,32 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4059,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4092,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4116,17 +4128,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4136,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4174,32 +4186,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4207,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4231,37 +4247,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4289,32 +4305,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4322,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4346,17 +4366,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4366,12 +4386,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4437,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4476,7 +4496,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4519,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4552,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4576,37 +4600,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4691,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4721,7 +4745,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4806,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4836,7 +4860,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4921,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4951,7 +4975,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4959,22 +4983,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5007,12 +5031,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5026,47 +5050,737 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>12/14</t>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,12 +709,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,14 +823,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,14 +2481,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,12 +2967,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,14 +4143,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4315,24 +4315,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:36</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4424,32 +4424,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4481,17 +4485,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4501,12 +4505,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4549,24 +4553,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4576,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,12 +4629,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4658,32 +4662,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4691,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4715,17 +4723,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4735,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4773,32 +4781,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -4806,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4830,17 +4842,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4850,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4888,32 +4900,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4921,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4945,37 +4961,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5003,32 +5019,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5036,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5060,17 +5080,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5080,12 +5100,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5118,32 +5138,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5151,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5175,37 +5199,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5381,7 +5405,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5435,7 +5459,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5496,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5550,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5655,12 +5679,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5726,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5775,12 +5799,472 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,14 +1176,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,14 +1414,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,14 +1767,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>79.3</t>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,14 +2719,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,14 +3076,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>79.3</t>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,22 +3552,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,14 +4738,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>77.7</t>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,14 +4857,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>79.3</t>
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5041,12 +5041,12 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5257,32 +5257,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5290,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5314,17 +5318,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5334,12 +5338,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5372,32 +5376,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5405,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5429,37 +5437,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5487,32 +5495,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5520,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5544,17 +5556,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5564,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5602,32 +5614,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -5635,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5659,32 +5675,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.5</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5717,32 +5733,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -5750,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,17 +5794,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5794,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5832,32 +5852,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5865,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5913,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5909,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5971,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -5980,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6004,37 +6032,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6149,7 +6177,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6264,7 +6292,697 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>69.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6090,32 +6090,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6123,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6151,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,17 +6171,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6205,32 +6209,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6238,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,37 +6270,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6353,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6468,7 +6476,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6522,7 +6530,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6698,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6752,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6862,7 +6870,7 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
@@ -6928,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6986,6 +6994,236 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:42</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC57"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5862,24 +5862,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5981,24 +5981,24 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6100,24 +6100,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6176,12 +6176,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6219,12 +6219,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6328,32 +6328,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6361,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,17 +6389,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6405,12 +6409,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6443,32 +6447,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6476,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6500,37 +6508,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6558,32 +6566,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -6591,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6615,17 +6627,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6635,12 +6647,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>70.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6706,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6745,7 +6757,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6760,7 +6772,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6833,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6870,12 +6882,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6948,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6990,7 +7002,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7051,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7105,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7215,12 +7227,472 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4391,12 +4391,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6338,24 +6338,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6457,24 +6457,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6533,12 +6533,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.2</t>
+          <t>69.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6685,32 +6685,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6718,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6742,17 +6746,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6762,17 +6766,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6833,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6948,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6987,7 +6991,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7063,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7178,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7232,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7408,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7457,12 +7461,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7527,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7638,7 +7642,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,17 +7686,132 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB61" s="2" t="inlineStr">
-        <is>
-          <t>77.7</t>
-        </is>
-      </c>
-      <c r="AC61" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>77.8</t>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,14 +1648,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,14 +2957,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>77.8</t>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,14 +3433,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,14 +4619,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>77.8</t>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,14 +4976,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,14 +5809,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>77.8</t>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,14 +5928,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>78.5</t>
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6290,17 +6290,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6576,24 +6576,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>69.5</t>
+          <t>68.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6695,12 +6695,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6771,12 +6771,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6804,32 +6804,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6837,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6865,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6923,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -6952,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,17 +6984,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6996,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7034,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7067,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,37 +7103,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7149,32 +7161,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7182,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7206,17 +7222,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7226,17 +7242,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7352,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7351,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7642,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7691,12 +7707,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7704,22 +7720,22 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A67983D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:40</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7752,12 +7768,12 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7771,47 +7787,622 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>15:40</t>
         </is>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>79.3</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
         <is>
           <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,14 +1886,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>76.5</t>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,14 +2124,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>76.5</t>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,17 +4024,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,17 +4143,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,14 +5214,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,17 +5333,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,14 +6047,14 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
           <t>76.5</t>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,14 +6166,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6285,17 +6285,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,7 +6404,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,17 +6528,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6766,17 +6766,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,14 +6880,14 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
           <t>76.5</t>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7171,19 +7171,19 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7280,32 +7280,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -7313,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7337,17 +7341,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7357,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7395,32 +7399,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7428,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,17 +7460,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7472,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7518,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7543,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,32 +7579,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7625,32 +7637,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7658,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,17 +7698,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7702,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,7 +7828,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7888,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8003,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8042,7 +8058,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8118,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8233,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8295,22 +8311,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A08953A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8343,12 +8359,12 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8362,47 +8378,852 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:22</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>76.0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
-        <is>
-          <t>6/14</t>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>77.8</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,22 +4976,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,22 +5928,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,17 +6166,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,22 +6761,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,17 +7361,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7647,24 +7647,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,22 +7713,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7756,32 +7756,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7789,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7817,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7833,17 +7837,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7871,32 +7875,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -7904,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,27 +7936,27 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
@@ -7986,32 +7994,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:58</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8019,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,17 +8055,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8063,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8101,32 +8113,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8134,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8158,37 +8174,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8216,32 +8232,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8249,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8273,37 +8293,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8331,32 +8351,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8364,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8388,32 +8412,32 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8446,32 +8470,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -8479,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8503,17 +8531,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8523,17 +8551,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8622,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8633,7 +8661,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8648,7 +8676,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8737,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8763,7 +8791,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8852,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8939,7 +8967,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9054,7 +9082,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9098,17 +9126,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9116,22 +9144,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17:15</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9169,7 +9197,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9183,47 +9211,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>76.6</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>68.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>77.7</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>10/14</t>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1539,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,17 +2838,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,17 +4024,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,22 +4143,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4381,22 +4381,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,17 +5333,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5452,22 +5452,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5576,17 +5576,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5690,17 +5690,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6285,22 +6285,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6404,22 +6404,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6523,22 +6523,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6642,17 +6642,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7237,22 +7237,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7317,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7475,22 +7475,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,22 +7832,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8075,17 +8075,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8373,12 +8373,12 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8480,24 +8480,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8507,7 +8507,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8589,32 +8589,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8622,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8646,17 +8650,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8666,17 +8670,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8704,32 +8708,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8737,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8761,37 +8769,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8819,32 +8827,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -8852,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8876,32 +8888,32 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8934,32 +8946,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8967,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8991,37 +9007,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9049,32 +9065,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9082,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9106,37 +9126,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9164,32 +9184,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9197,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9221,37 +9245,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9279,32 +9303,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -9312,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9336,32 +9364,32 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>68.5</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9394,32 +9422,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9427,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9451,17 +9483,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9471,17 +9503,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9574,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9596,7 +9628,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9657,7 +9689,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9696,7 +9728,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9711,7 +9743,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9772,7 +9804,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9887,7 +9919,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9941,7 +9973,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10002,7 +10034,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10046,17 +10078,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10117,7 +10149,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10175,6 +10207,811 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,17 +942,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,22 +3314,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,17 +4024,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,22 +5214,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5333,17 +5333,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5581,12 +5581,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6052,17 +6052,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,22 +6166,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6246,7 +6246,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6761,22 +6761,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6885,17 +6885,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,22 +6999,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,17 +7594,17 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7713,22 +7713,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7951,22 +7951,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8031,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8189,22 +8189,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8903,17 +8903,17 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9313,24 +9313,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9432,24 +9432,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>78.4</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9541,32 +9541,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9574,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9598,37 +9602,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9656,32 +9660,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9689,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9713,17 +9721,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9733,17 +9741,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9771,32 +9779,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9804,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,37 +9840,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9886,32 +9898,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -9919,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9943,37 +9959,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10001,32 +10017,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10034,7 +10054,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10058,17 +10078,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10078,17 +10098,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10116,32 +10136,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:37</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10149,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10173,37 +10197,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10379,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10461,32 +10485,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10494,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10518,32 +10546,32 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA85" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10609,7 +10637,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10663,7 +10691,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10773,7 +10801,7 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>70.4</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10839,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10893,7 +10921,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10901,22 +10929,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10949,12 +10977,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10968,47 +10996,622 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>78.2</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>10/14</t>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,17 +3433,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4386,17 +4386,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4619,22 +4619,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,17 +4976,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5651,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5695,12 +5695,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5809,22 +5809,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5928,17 +5928,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6528,17 +6528,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6647,12 +6647,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6766,17 +6766,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7480,17 +7480,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7718,17 +7718,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7832,22 +7832,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7956,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8308,17 +8308,17 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8913,7 +8913,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9141,22 +9141,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9265,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9384,12 +9384,12 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9622,17 +9622,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9736,17 +9736,17 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9979,17 +9979,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10158,12 +10158,12 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10495,12 +10495,12 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10604,32 +10604,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10637,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10661,17 +10665,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10681,17 +10685,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -10719,32 +10723,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -10752,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10776,17 +10784,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10796,12 +10804,12 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>70.4</t>
+          <t>70.5</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
@@ -10834,32 +10842,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -10867,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10891,37 +10903,37 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA88" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>77.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10949,32 +10961,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -10982,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11006,17 +11022,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11026,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11064,32 +11080,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11097,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11121,17 +11141,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11141,17 +11161,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11179,32 +11199,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11212,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11236,32 +11260,32 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11327,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11381,7 +11405,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11481,7 +11505,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11496,7 +11520,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11606,12 +11630,357 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.9</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
           <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>77.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,17 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4624,17 +4624,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5814,17 +5814,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7555,7 +7555,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7599,17 +7599,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7837,17 +7837,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8194,17 +8194,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8432,17 +8432,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8561,7 +8561,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8908,17 +8908,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,17 +9146,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9860,17 +9860,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10108,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10217,17 +10217,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10522,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10566,17 +10566,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11318,32 +11318,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11351,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11375,17 +11379,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11395,17 +11399,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -11433,32 +11437,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11466,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11490,17 +11498,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11510,17 +11518,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11548,32 +11556,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11581,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11605,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11625,17 +11637,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>80.9</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11663,32 +11675,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -11696,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11720,17 +11736,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11740,17 +11756,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>77.4</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11811,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11926,7 +11942,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11970,17 +11986,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-182路.xlsx
+++ b/data/export/2026-09-28-182路.xlsx
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,17 +4981,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5889,7 +5889,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5933,17 +5933,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6171,17 +6171,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6538,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8313,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8432,17 +8432,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8799,7 +8799,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9037,7 +9037,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9151,7 +9151,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9741,17 +9741,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9816,7 +9816,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9860,17 +9860,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10457,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11236,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11280,17 +11280,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11518,17 +11518,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11685,12 +11685,12 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11794,32 +11794,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11827,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11851,17 +11855,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11871,17 +11875,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11909,32 +11913,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11942,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11966,17 +11974,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11986,17 +11994,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
